--- a/artfynd/A 52177-2021 artfynd.xlsx
+++ b/artfynd/A 52177-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117664462</v>
+        <v>117664454</v>
       </c>
       <c r="B2" t="n">
-        <v>90519</v>
+        <v>56499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762702</v>
+        <v>762698</v>
       </c>
       <c r="R2" t="n">
-        <v>7308444</v>
+        <v>7308480</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,6 +757,11 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,17 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117664454</v>
+        <v>117664462</v>
       </c>
       <c r="B3" t="n">
-        <v>56499</v>
+        <v>90519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762698</v>
+        <v>762702</v>
       </c>
       <c r="R3" t="n">
-        <v>7308480</v>
+        <v>7308444</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -859,11 +864,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52177-2021 artfynd.xlsx
+++ b/artfynd/A 52177-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117664454</v>
       </c>
       <c r="B2" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>117664462</v>
       </c>
       <c r="B3" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52177-2021 artfynd.xlsx
+++ b/artfynd/A 52177-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117664462</v>
+        <v>117663042</v>
       </c>
       <c r="B2" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762702</v>
+        <v>762726</v>
       </c>
       <c r="R2" t="n">
-        <v>7308444</v>
+        <v>7308406</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,54 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117664454</v>
+        <v>117664462</v>
       </c>
       <c r="B3" t="n">
-        <v>56500</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762698</v>
+        <v>762702</v>
       </c>
       <c r="R3" t="n">
-        <v>7308480</v>
+        <v>7308444</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -859,11 +849,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,10 +866,425 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118814657</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>762671</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7308858</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121056470</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107695</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221705</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängskovall</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fällforsberget ca 500 m NNV om pkt 87,61, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>762487</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7308594</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1995-07-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1995-07-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>berghällar</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4528975</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>762606</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7308271</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1992-08-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1992-08-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Sydbrant, klipphyllor</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117660300</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>762720</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7308402</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52177-2021 artfynd.xlsx
+++ b/artfynd/A 52177-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117663042</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664462</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814657</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121056470</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4528975</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,8 +1315,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117660300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>